--- a/data/kindergarten/data.xlsx
+++ b/data/kindergarten/data.xlsx
@@ -1372,7 +1372,7 @@
         <v>134.052507</v>
       </c>
       <c r="D38" t="str">
-        <v>光華幼稚園</v>
+        <v>認定こども園光華幼稚園</v>
       </c>
       <c r="E38" t="str">
         <v>高松市瓦町一丁目13-8</v>
@@ -1398,7 +1398,7 @@
         <v>134.052686</v>
       </c>
       <c r="D39" t="str">
-        <v>くにとう幼稚園</v>
+        <v>認定こども園くにとう幼稚園</v>
       </c>
       <c r="E39" t="str">
         <v>高松市伏石町1611</v>
@@ -1424,7 +1424,7 @@
         <v>134.095292</v>
       </c>
       <c r="D40" t="str">
-        <v>屋島教会幼稚園</v>
+        <v>幼稚園型認定こども園屋島教会幼稚園</v>
       </c>
       <c r="E40" t="str">
         <v>高松市屋島西町1392-7</v>

--- a/data/kindergarten/data.xlsx
+++ b/data/kindergarten/data.xlsx
@@ -800,13 +800,13 @@
         <v>134.137129</v>
       </c>
       <c r="D16" t="str">
-        <v>高松市立田井幼稚園（令和2年4月1日から休園）</v>
+        <v>高松市立田井こども園</v>
       </c>
       <c r="E16" t="str">
         <v>高松市牟礼町牟礼1243-2</v>
       </c>
       <c r="F16" t="str">
-        <v>087-845-3701</v>
+        <v>087-845-5411</v>
       </c>
       <c r="G16" t="str">
         <v>http://www.city.takamatsu.kagawa.jp/kurashi/kosodate/youchien_hoiku/kodomoen/chiiki_suishin/gaiyou.html</v>

--- a/data/kindergarten/data.xlsx
+++ b/data/kindergarten/data.xlsx
@@ -806,7 +806,7 @@
         <v>高松市牟礼町牟礼1243-2</v>
       </c>
       <c r="F16" t="str">
-        <v>087-845-5411</v>
+        <v/>
       </c>
       <c r="G16" t="str">
         <v>http://www.city.takamatsu.kagawa.jp/kurashi/kosodate/youchien_hoiku/kodomoen/chiiki_suishin/gaiyou.html</v>
@@ -826,13 +826,13 @@
         <v>134.148384</v>
       </c>
       <c r="D17" t="str">
-        <v>高松市立大町幼稚園</v>
+        <v>旧高松市立大町幼稚園</v>
       </c>
       <c r="E17" t="str">
         <v>高松市牟礼町牟礼100-1</v>
       </c>
       <c r="F17" t="str">
-        <v>087-845-5718</v>
+        <v/>
       </c>
       <c r="G17" t="str">
         <v>http://www.city.takamatsu.kagawa.jp/kurashi/kosodate/youchien_hoiku/kodomoen/chiiki_suishin/gaiyou.html</v>
